--- a/output/pdf_financials_xlsx/DBO.xlsx
+++ b/output/pdf_financials_xlsx/DBO.xlsx
@@ -2064,13 +2064,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.006</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.732</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.105</v>
       </c>
     </row>
     <row r="93">
@@ -3585,7 +3585,11 @@
           <t>Share-based payment reserve 11.3</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>1.006</v>
       </c>

--- a/output/pdf_financials_xlsx/DBO.xlsx
+++ b/output/pdf_financials_xlsx/DBO.xlsx
@@ -502,20 +502,14 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.0121</v>
       </c>
     </row>
     <row r="6">
@@ -546,20 +540,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -568,20 +556,14 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.0126</v>
       </c>
     </row>
     <row r="9">
@@ -590,20 +572,14 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -612,20 +588,14 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.0126</v>
       </c>
     </row>
     <row r="11">
@@ -656,20 +626,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -678,20 +642,14 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -700,20 +658,14 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -722,20 +674,14 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -766,20 +712,14 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0.013</v>
       </c>
     </row>
     <row r="18">
@@ -854,20 +794,14 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -876,20 +810,14 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1008,20 +936,14 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.006</v>
       </c>
     </row>
     <row r="29">
@@ -1490,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>2.011</v>
       </c>
     </row>
     <row r="57">
@@ -1506,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>2.011</v>
       </c>
     </row>
     <row r="58">
@@ -1612,13 +1534,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.644</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.223</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.542</v>
       </c>
     </row>
     <row r="65">
@@ -1660,13 +1582,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.806</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.954</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.101</v>
       </c>
     </row>
     <row r="68">
@@ -2188,20 +2110,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0.006</v>
       </c>
     </row>
     <row r="101">
@@ -2342,20 +2258,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.0113</v>
       </c>
     </row>
     <row r="108">
@@ -2430,20 +2340,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>-0.662</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>-0.658</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0.005</v>
       </c>
     </row>
     <row r="112">
@@ -2936,20 +2840,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>-0.662</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>-0.658</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>-0.005</v>
       </c>
     </row>
     <row r="135">
@@ -2985,7 +2883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3683,6 +3581,393 @@
         <v>23.713</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Amortization of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" s="5" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Amortization of intangible assets</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Amortization of other assets</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" s="5" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Write-off of property, plant and equipment                                           4            9</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Share-based payment expense</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.0113</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Additions to property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.662</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.658</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Disposals of property, plant and equipment                   —            6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Additions to intangible assets</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-0.243</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-0.321</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Repayment of long-term debt                        —            (13)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Shares issued</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" s="5" t="n">
+        <v>23.026</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.0111</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>8,832             6,685</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cost of goods sold excluding amortization</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>3.295</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>3.964</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.0123</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>8,832             6,685</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Amortization related to cost of goods sold 7,</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.0121</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Selling and marketing</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>4.918</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>5.629</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.0124</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" s="5" t="n">
+        <v>2.893</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>3.436</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Research and development</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.0126</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Loss before income taxes                                                 (6,557)             (6,151)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
